--- a/tools/_out/brennancad_20261021/regen/stage/straight/DesignTable_5406_SW2.xlsx
+++ b/tools/_out/brennancad_20261021/regen/stage/straight/DesignTable_5406_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF32"/>
+  <dimension ref="A1:AF33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4098,6 +4098,124 @@
       <c r="AF32" t="inlineStr">
         <is>
           <t>5406-32-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5406-40-32</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.73205</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.40977</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.1374</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.81954</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.1374</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.40977</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.30977</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.1696</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>5406-40-32</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Pipe Reducer Bushing (male NPTF x female NPTF), 2 1/2-8 NPTF x 2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>5406</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2 1/2-8 NPTF</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C2HEX@HEX, L2@DRIVE, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION), hex head behind it; female NPTF port from the hex face: Air-Way tap drill to MS51503 P1 max per pipe dash (2405 table), helical thread over P1; Brennan 5405-08-08 STEP confirms the P1 rule for 1/2 NPTF (VERIFIED -08 only); Air-Way publishes no through-bore for the bushing -&gt; the tap drill is carried through to the male tip (ASSUMPTION, machined-bushing practice); wall between the female thread crests and the male thread roots checked per row; -40 PIPE END (2-1/2-8 NPTF) IS BRENNAN-MEASURED, NOT ASME B1.20.1 (user 2026-10-02: Brennan-measured threads accepted for -40): male end - pitch dia at the tip E0 2.71954 = the Brennan blank cone 2.7769 (5404-40-40 / 5406-40-32 / 2501-40-40-FG STEPs) - 0.4589 P (the Brennan blank sits 0.4585-0.4595 P above ASME E0 at all 8 library sizes -04..-32, ASSUMED to hold at -40), crest E0 + 0.8P, taper 1.7899deg, thread length L2 1.1374 from D = E0 + 0.8P + (L2 - 2P)/16 with pipe OD D 2.875 (Brennan collar), end length 1.515 (measured on all four Brennan -40 male ends); female port - tap drill 2.729 and thread depth 1.0443 = the Brennan 5000-40-40 tapered port (no separate drill: the 2.729 bore runs through); 8 threads per inch = Brennan TFA catalog callout 2-1/2-8; single manufacturer, ASSUMED</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | Brennan CAD record 5406-40-32 (PARTcommunity / CADENAS, C2HEX@HEX=C, L2@DRIVE=L, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>5406-40-32</t>
         </is>
       </c>
     </row>
